--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>287</v>
+        <v>385</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>142</v>
+        <v>354</v>
       </c>
       <c r="D3">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>385</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>426</v>
